--- a/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mood/current_mood_vs_recommendation_type.xlsx
+++ b/smartshop/EvidenceBasedAdaptiveUI/reports/02_exploratory_data_analysis/tables/mood/current_mood_vs_recommendation_type.xlsx
@@ -465,13 +465,13 @@
         <v>5</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -519,10 +519,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>3</v>
@@ -538,16 +538,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="D6" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="7">
@@ -560,13 +560,13 @@
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D7" t="n">
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -598,10 +598,10 @@
         <v>10</v>
       </c>
       <c r="C9" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>3</v>
